--- a/output/Humanitarian_icons.xlsx
+++ b/output/Humanitarian_icons.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Humanitarian Icons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Humanitarian Icons" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Humanitarian Icons'!$1:$1</definedName>
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Camp coordination and camp management</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Early recovery</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Emergency telecommunications</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Food security</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Clusters</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -594,12 +594,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Clusters</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Child care child friendly</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Clusters</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Child protection</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -628,12 +628,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Clusters</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -645,12 +645,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Clusters</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Fishery</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Child care child friendly</t>
+          <t>Multi-cluster sector</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Child protection</t>
+          <t>Rule of law and justice</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Coordination</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Anticipatory action</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fishery</t>
+          <t>Cold wave</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -764,12 +764,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Logistics and telecommunications</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Multi-cluster sector</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Rule of law and justice</t>
+          <t>Drought</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Shelter, land and site coordination</t>
+          <t>Epidemic</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Anticipatory action</t>
+          <t>Famine</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cold wave</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Flash flood</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Drought</t>
+          <t>Heatwave</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Heavy rain</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Epidemic</t>
+          <t>Humanitarian access</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Famine</t>
+          <t>Insect infestation</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Internally displaced</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Flash flood</t>
+          <t>Landslide mudslide</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Flood</t>
+          <t>Locust infestation</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Heatwave</t>
+          <t>Population return</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Heavy rain</t>
+          <t>Poverty</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Humanitarian access</t>
+          <t>Refugee</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Insect infestation</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Internally displaced</t>
+          <t>Snow avalanche</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Landslide mudslide</t>
+          <t>Snowfall</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Locust infestation</t>
+          <t>Storm</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Population return</t>
+          <t>Storm surge</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Poverty</t>
+          <t>Technological disaster</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Refugee</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Tsunami</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Snow avalanche</t>
+          <t>Violent wind</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Snowfall</t>
+          <t>Volcano</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Storm</t>
+          <t>Worm infestation</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Storm surge</t>
+          <t>Debris management</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Technological disaster</t>
+          <t>Livelihood</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Livestock</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tsunami</t>
+          <t>Population growth</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Violent wind</t>
+          <t>Reconstruction</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Volcano</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Worm infestation</t>
+          <t>Rural exodus</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Debris management</t>
+          <t>Trade and market</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Livelihood</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Livestock</t>
+          <t>Urban rural</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Population growth</t>
+          <t>Affected population</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Reconstruction</t>
+          <t>Child combatant</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Children</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Rural exodus</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Trade and market</t>
+          <t>Drowned</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Elderly</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Urban rural</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Affected population</t>
+          <t>Infant</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Child combatant</t>
+          <t>Injured</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Dead</t>
+          <t>National army</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Drowned</t>
+          <t>Peacekeeping force</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Elderly</t>
+          <t>People affected</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>People covered</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Indigenous people</t>
+          <t>People in need</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Infant</t>
+          <t>People in need 2</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Injured</t>
+          <t>People reached</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>People targeted</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>National army</t>
+          <t>People targeted 2</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Peacekeeping force</t>
+          <t>People with physical impairments</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>People affected</t>
+          <t>Person 1</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>People covered</t>
+          <t>Person 2</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>People in need</t>
+          <t>Pregnant</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>People in need 2</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>People reached</t>
+          <t>Resettlement</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>People targeted</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>People targeted 2</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>People with physical impairments</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Person 1</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Person 2</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Pregnant</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -1971,12 +1971,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>Film</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Resettlement</t>
+          <t>Live geoservices</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Advocacy</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>P-code</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2056,12 +2056,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Cash transfer</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Civil military coordination</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Community engagement</t>
+          <t>Blanket</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Coordinated assessment</t>
+          <t>Bottled water</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Bucket</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>Detergent</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Gap analysis</t>
+          <t>Flour</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Humanitarian programme cycle</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Information management</t>
+          <t>Kitchen set</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Mattress</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Medical supply</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Mosquito net</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Non food items</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2345,12 +2345,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Non food items 2</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Needs assessment</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Partnership</t>
+          <t>Plastic sheeting</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Relief goods</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Preparedness</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Public information</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Soap</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Stove</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Scale down operation</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Scale up operation</t>
+          <t>Tarpaulin</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Search and rescue</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Services and tools</t>
+          <t>Vaccine</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -2549,12 +2549,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Sexual and reproductive health</t>
+          <t>Borehole</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Staff management</t>
+          <t>Communal latrine</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Top ranking</t>
+          <t>Latrine cabin</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Potable water</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Potable water source</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Sanitation</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -2651,12 +2651,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Solid waste</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Spring water</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>Submersible pump</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Live geoservices</t>
+          <t>Toilet</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Water source</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Water trucking</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>P-code</t>
+          <t>IDP refugee camp</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Permanent camp</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Spontaneous site</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Temporary camp</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Blanket</t>
+          <t>Transition site</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Bottled water</t>
+          <t>Abduction kidnapping</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Bucket</t>
+          <t>Arrest detention</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Detergent</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Flour</t>
+          <t>Carjacking</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Confined</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Kitchen set</t>
+          <t>Dangerous area</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Mattress</t>
+          <t>Forced entry</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Medical supply</t>
+          <t>Forced recruitment</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Gender based violence</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Mosquito net</t>
+          <t>Harassment intimidation</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Non food items</t>
+          <t>House burned</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Non food items 2</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Murder</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Plastic sheeting</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -3127,12 +3127,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Relief goods</t>
+          <t>Sexual violence</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Border crossing</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Checkpoint</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -3178,12 +3178,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Soap</t>
+          <t>Earthmound</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Stove</t>
+          <t>Military gate</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Observation tower</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Tarpaulin</t>
+          <t>Physical closure</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Tent</t>
+          <t>Road barrier</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Vaccine</t>
+          <t>Roadblock</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Borehole</t>
+          <t>Airport affected</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Communal latrine</t>
+          <t>Airport destroyed</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Latrine cabin</t>
+          <t>Airport not affected</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Potable water</t>
+          <t>Bridge affected</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Potable water source</t>
+          <t>Bridge destroyed</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Sanitation</t>
+          <t>Bridge not affected</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Building facility affected</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Solid waste</t>
+          <t>Building facility destroyed</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Spring water</t>
+          <t>Building facility not affected</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Submersible pump</t>
+          <t>Destroyed</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Health facility affected</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Water source</t>
+          <t>Health facility destroyed</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Water trucking</t>
+          <t>Health facility not affected</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>IDP refugee camp</t>
+          <t>House affected</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Permanent camp</t>
+          <t>House destroyed</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>House not affected</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Spontaneous site</t>
+          <t>Not affected</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Temporary camp</t>
+          <t>Port affected</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Transition site</t>
+          <t>Port destroyed</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Abduction kidnapping</t>
+          <t>Port not affected</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Arrest detention</t>
+          <t>Power electricity affected</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Power electricity not affected</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Power outage</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -3671,12 +3671,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Carjacking</t>
+          <t>Road affected</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Confined</t>
+          <t>Road destroyed</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Dangerous area</t>
+          <t>Road not affected</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Forced entry</t>
+          <t>School affected</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Forced recruitment</t>
+          <t>School destroyed</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Gender based violence</t>
+          <t>School not affected</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Harassment intimidation</t>
+          <t>Assembly point</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -3790,12 +3790,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>House burned</t>
+          <t>Buddhist temple</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Murder</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Sexual violence</t>
+          <t>Community building</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Border crossing</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Checkpoint</t>
+          <t>Diplomatic mission</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Earthmound</t>
+          <t>Distribution site</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Military gate</t>
+          <t>Food warehouse</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Observation tower</t>
+          <t>Government office</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Physical closure</t>
+          <t>Health facility</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Road barrier</t>
+          <t>Health post</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Roadblock</t>
+          <t>Hindu temple</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Airport affected</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Airport destroyed</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Airport not affected</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Bridge affected</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Bridge destroyed</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Bridge not affected</t>
+          <t>Mobile clinic</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -4113,12 +4113,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Building facility affected</t>
+          <t>Mosque</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Building facility destroyed</t>
+          <t>NGO office</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Building facility not affected</t>
+          <t>Oil facility</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Damaged affected</t>
+          <t>Police station</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Destroyed</t>
+          <t>Power electricity</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Health facility affected</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Health facility destroyed</t>
+          <t>UN compound office</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Health facility not affected</t>
+          <t>University</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>House affected</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>House destroyed</t>
+          <t>Airport military</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>House not affected</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -4300,12 +4300,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Not affected</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Port affected</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Port destroyed</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Port not affected</t>
+          <t>Ferry</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -4368,12 +4368,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Power electricity affected</t>
+          <t>Gas station</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Power electricity not affected</t>
+          <t>Helicopter</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Power outage</t>
+          <t>Helipad</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Road affected</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Road destroyed</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Road not affected</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>School affected</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>School destroyed</t>
+          <t>Truck</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -4504,12 +4504,12 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>School not affected</t>
+          <t>Tunnel</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Assembly point</t>
+          <t>UN vehicle</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Buddhist temple</t>
+          <t>Cell tower</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Fax</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Community building</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Diplomatic mission</t>
+          <t>Mobile phone</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Distribution site</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Food warehouse</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Government office</t>
+          <t>Remote support</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Health facility</t>
+          <t>Satellite dish</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Health post</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Hindu temple</t>
+          <t>Walkie talkie</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Work from home</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Add document</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Mobile clinic</t>
+          <t>AI chat</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Mosque</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>NGO office</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Oil facility</t>
+          <t>Blog</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Police station</t>
+          <t>Bookmark</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Power electricity</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Checked mail</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>UN compound office</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>CSV file</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>Delete account</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Airport military</t>
+          <t>DOCX file</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Expand down</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Ferry</t>
+          <t>Expand left</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Gas station</t>
+          <t>Expand right</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Helicopter</t>
+          <t>Expand up</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Helipad</t>
+          <t>Favourite</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Truck</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Tunnel</t>
+          <t>Hidden</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>UN vehicle</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Cell tower</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>More options</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Next item</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Fax</t>
+          <t>Not secured</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Out of platform</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Mobile phone</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>PDF file</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Remote support</t>
+          <t>Previous item</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Satellite dish</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -5473,12 +5473,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Walkie talkie</t>
+          <t>Remove document</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Work from home</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Add document</t>
+          <t>Secured</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>AI chat</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>See</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Blog</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Bookmark</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Checked mail</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Trending</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>CSV file</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Delete account</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>DOCX file</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Validate account</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>XLSX file</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Exit cancel</t>
+          <t>ZIP compressed</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Expand down</t>
+          <t>Bacteria</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Expand left</t>
+          <t>Case management</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Expand right</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Expand up</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Favourite</t>
+          <t>Handwashing</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Health worker</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Hospital bed</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Infected</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Infection control</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Hidden</t>
+          <t>Life saving</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Mask</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Not infected</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>More options</t>
+          <t>Physical distancing</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Next item</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Not secured</t>
+          <t>Sanitizer</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Out of platform</t>
+          <t>Ventilator</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Airport closed</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>PDF file</t>
+          <t>Border closed</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Previous item</t>
+          <t>Bridge closed</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Building closed</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>House lockdown</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Remove document</t>
+          <t>Location lockdown</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Market closed</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Port closed</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Road closed</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -6289,12 +6289,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Secured</t>
+          <t>School closed</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -6306,12 +6306,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Advocacy</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>See</t>
+          <t>Agile</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Cash transfer</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Civil military coordination</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Community engagement</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Fund</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Gap analysis</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Humanitarian programme cycle</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Validate account</t>
+          <t>Information management</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Warning error</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>XLSX file</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>ZIP compressed</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Bacteria</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Case management</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -6629,12 +6629,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Needs assessment</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Handwashing</t>
+          <t>Partnership</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Health worker</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Hospital bed</t>
+          <t>Preparedness</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Infected</t>
+          <t>Public information</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Infection control</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -6748,12 +6748,12 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Life saving</t>
+          <t>Scale down operation</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Scale up operation</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t>Search and rescue</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Not infected</t>
+          <t>Services and tools</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Physical distancing</t>
+          <t>Staff management</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>Top ranking</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Sanitizer</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Camp coordination and camp management</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Ventilator</t>
+          <t>Coordinated assessment</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Damaged affected</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Airport closed</t>
+          <t>Early recovery</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Border closed</t>
+          <t>Emergency telecommunications</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed</t>
+          <t>Exit cancel</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Building closed</t>
+          <t>Food security</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -6986,12 +6986,12 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>House lockdown</t>
+          <t>Indigenous people</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Location lockdown</t>
+          <t>Logistics and telecommunications</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Market closed</t>
+          <t>Sexual and reproductive health</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Port closed</t>
+          <t>Shelter, land and site coordination</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Road closed</t>
+          <t>Warning error</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -7071,12 +7071,12 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>School closed</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">

--- a/output/Humanitarian_icons.xlsx
+++ b/output/Humanitarian_icons.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Camp coordination and camp management</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Early recovery</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Emergency telecommunications</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Food security</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -577,12 +577,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Clusters</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -594,12 +594,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Clusters</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Child care child friendly</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Clusters</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Child protection</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -628,12 +628,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Clusters</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Coordination</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -645,12 +645,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Other sectors</t>
+          <t>Clusters</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Fishery</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Multi-cluster sector</t>
+          <t>Child care child friendly</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Rule of law and justice</t>
+          <t>Child protection</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Safety and security</t>
+          <t>Coordination</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Anticipatory action</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cold wave</t>
+          <t>Fishery</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -764,12 +764,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Logistics and telecommunications</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Multi-cluster sector</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Drought</t>
+          <t>Rule of law and justice</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Safety and security</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Disasters, hazards and crises</t>
+          <t>Other sectors</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Epidemic</t>
+          <t>Shelter, land and site coordination</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Famine</t>
+          <t>Anticipatory action</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Cold wave</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Flash flood</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Flood</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Heatwave</t>
+          <t>Drought</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Heavy rain</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Humanitarian access</t>
+          <t>Epidemic</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Insect infestation</t>
+          <t>Famine</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Internally displaced</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Landslide mudslide</t>
+          <t>Flash flood</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Locust infestation</t>
+          <t>Flood</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Population return</t>
+          <t>Heatwave</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Poverty</t>
+          <t>Heavy rain</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Refugee</t>
+          <t>Humanitarian access</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Insect infestation</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Snow avalanche</t>
+          <t>Internally displaced</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Snowfall</t>
+          <t>Landslide mudslide</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Storm</t>
+          <t>Locust infestation</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Storm surge</t>
+          <t>Population return</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Technological disaster</t>
+          <t>Poverty</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Refugee</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Tsunami</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Violent wind</t>
+          <t>Snow avalanche</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Volcano</t>
+          <t>Snowfall</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Worm infestation</t>
+          <t>Storm</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Debris management</t>
+          <t>Storm surge</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Livelihood</t>
+          <t>Technological disaster</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Livestock</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Population growth</t>
+          <t>Tsunami</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1342,12 +1342,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Reconstruction</t>
+          <t>Violent wind</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Volcano</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1376,12 +1376,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic and development</t>
+          <t>Disasters, hazards and crises</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Rural exodus</t>
+          <t>Worm infestation</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Trade and market</t>
+          <t>Debris management</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Livelihood</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Urban rural</t>
+          <t>Livestock</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Affected population</t>
+          <t>Population growth</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Child combatant</t>
+          <t>Reconstruction</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Dead</t>
+          <t>Rural exodus</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Drowned</t>
+          <t>Trade and market</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Elderly</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Socioeconomic and development</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Urban rural</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Infant</t>
+          <t>Affected population</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Injured</t>
+          <t>Child combatant</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Children</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>National army</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Peacekeeping force</t>
+          <t>Drowned</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>People affected</t>
+          <t>Elderly</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>People covered</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>People in need</t>
+          <t>Indigenous people</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>People in need 2</t>
+          <t>Infant</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>People reached</t>
+          <t>Injured</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>People targeted</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>People targeted 2</t>
+          <t>National army</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>People with physical impairments</t>
+          <t>Peacekeeping force</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Person 1</t>
+          <t>People affected</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Person 2</t>
+          <t>People covered</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Pregnant</t>
+          <t>People in need</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Rebel</t>
+          <t>People in need 2</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Resettlement</t>
+          <t>People reached</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>People targeted</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>People targeted 2</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>People with physical impairments</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Person 1</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Person 2</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Pregnant</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -1971,12 +1971,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>Rebel</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Live geoservices</t>
+          <t>Resettlement</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>People</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Advocacy</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>P-code</t>
+          <t>Agile</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2056,12 +2056,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Cash transfer</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Product type</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Civil military coordination</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Blanket</t>
+          <t>Community engagement</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Bottled water</t>
+          <t>Coordinated assessment</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Bucket</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Detergent</t>
+          <t>Fund</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Flour</t>
+          <t>Gap analysis</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Humanitarian programme cycle</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Kitchen set</t>
+          <t>Information management</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Mattress</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Medical supply</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Mosquito net</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Non food items</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2345,12 +2345,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Non food items 2</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Needs assessment</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Plastic sheeting</t>
+          <t>Partnership</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Relief goods</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Preparedness</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Public information</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Soap</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Stove</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Scale down operation</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Tarpaulin</t>
+          <t>Scale up operation</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Tent</t>
+          <t>Search and rescue</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Food and non-food items</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Vaccine</t>
+          <t>Services and tools</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -2549,12 +2549,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Borehole</t>
+          <t>Sexual and reproductive health</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Communal latrine</t>
+          <t>Staff management</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Latrine cabin</t>
+          <t>Top ranking</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Activities strategy</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Potable water</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Potable water source</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Sanitation</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -2651,12 +2651,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Shower</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Solid waste</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Spring water</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Submersible pump</t>
+          <t>Film</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Toilet</t>
+          <t>Live geoservices</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Water source</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Water trucking</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>IDP refugee camp</t>
+          <t>P-code</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Permanent camp</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Spontaneous site</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Product type</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Temporary camp</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Transition site</t>
+          <t>Blanket</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Abduction kidnapping</t>
+          <t>Bottled water</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Arrest detention</t>
+          <t>Bucket</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Assault</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Detergent</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Carjacking</t>
+          <t>Flour</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Confined</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Dangerous area</t>
+          <t>Kitchen set</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Forced entry</t>
+          <t>Mattress</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Forced recruitment</t>
+          <t>Medical supply</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Gender based violence</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Harassment intimidation</t>
+          <t>Mosquito net</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>House burned</t>
+          <t>Non food items</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Non food items 2</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Murder</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Robbery</t>
+          <t>Plastic sheeting</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -3127,12 +3127,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Security and incident</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Sexual violence</t>
+          <t>Relief goods</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Border crossing</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Checkpoint</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -3178,12 +3178,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Earthmound</t>
+          <t>Soap</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Military gate</t>
+          <t>Stove</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Observation tower</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Physical closure</t>
+          <t>Tarpaulin</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Road barrier</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Physical barriers</t>
+          <t>Food and non-food items</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Roadblock</t>
+          <t>Vaccine</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Airport affected</t>
+          <t>Borehole</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Airport destroyed</t>
+          <t>Communal latrine</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Airport not affected</t>
+          <t>Latrine cabin</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Bridge affected</t>
+          <t>Potable water</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Bridge destroyed</t>
+          <t>Potable water source</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Bridge not affected</t>
+          <t>Sanitation</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Building facility affected</t>
+          <t>Shower</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Building facility destroyed</t>
+          <t>Solid waste</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Building facility not affected</t>
+          <t>Spring water</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Destroyed</t>
+          <t>Submersible pump</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Health facility affected</t>
+          <t>Toilet</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Health facility destroyed</t>
+          <t>Water source</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Water sanitation and hygiene</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Health facility not affected</t>
+          <t>Water trucking</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>House affected</t>
+          <t>IDP refugee camp</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>House destroyed</t>
+          <t>Permanent camp</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>House not affected</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Not affected</t>
+          <t>Spontaneous site</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Port affected</t>
+          <t>Temporary camp</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Port destroyed</t>
+          <t>Transition site</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Port not affected</t>
+          <t>Abduction kidnapping</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Power electricity affected</t>
+          <t>Arrest detention</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Power electricity not affected</t>
+          <t>Assault</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Power outage</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -3671,12 +3671,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Road affected</t>
+          <t>Carjacking</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Road destroyed</t>
+          <t>Confined</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Road not affected</t>
+          <t>Dangerous area</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>School affected</t>
+          <t>Forced entry</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>School destroyed</t>
+          <t>Forced recruitment</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>School not affected</t>
+          <t>Gender based violence</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Assembly point</t>
+          <t>Harassment intimidation</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -3790,12 +3790,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Buddhist temple</t>
+          <t>House burned</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Murder</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Robbery</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Security and incident</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Community building</t>
+          <t>Sexual violence</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Border crossing</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Diplomatic mission</t>
+          <t>Checkpoint</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Distribution site</t>
+          <t>Earthmound</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Food warehouse</t>
+          <t>Military gate</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Government office</t>
+          <t>Observation tower</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Health facility</t>
+          <t>Physical closure</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Health post</t>
+          <t>Road barrier</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Physical barriers</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Hindu temple</t>
+          <t>Roadblock</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Airport affected</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Airport destroyed</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>House</t>
+          <t>Airport not affected</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Bridge affected</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Bridge destroyed</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Mobile clinic</t>
+          <t>Bridge not affected</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -4113,12 +4113,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Mosque</t>
+          <t>Building facility affected</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -4130,12 +4130,12 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>NGO office</t>
+          <t>Building facility destroyed</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Oil facility</t>
+          <t>Building facility not affected</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Police station</t>
+          <t>Damaged affected</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Power electricity</t>
+          <t>Destroyed</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Health facility affected</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>UN compound office</t>
+          <t>Health facility destroyed</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>General infrastructure</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Health facility not affected</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>House affected</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Airport military</t>
+          <t>House destroyed</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>House not affected</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -4300,12 +4300,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Not affected</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Port affected</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Port destroyed</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Ferry</t>
+          <t>Port not affected</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -4368,12 +4368,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Gas station</t>
+          <t>Power electricity affected</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Helicopter</t>
+          <t>Power electricity not affected</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Helipad</t>
+          <t>Power outage</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Road affected</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Road destroyed</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Road not affected</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>School affected</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Truck</t>
+          <t>School destroyed</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -4504,12 +4504,12 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Tunnel</t>
+          <t>School not affected</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>UN vehicle</t>
+          <t>Assembly point</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Cell tower</t>
+          <t>Buddhist temple</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Computer</t>
+          <t>Building</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Fax</t>
+          <t>Clinic</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Community building</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Mobile phone</t>
+          <t>Diplomatic mission</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Distribution site</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Food warehouse</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Remote support</t>
+          <t>Government office</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Satellite dish</t>
+          <t>Health facility</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -4725,12 +4725,12 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Health post</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Walkie talkie</t>
+          <t>Hindu temple</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Telecommunications and technology</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Work from home</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>House</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Add document</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>AI chat</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Mobile clinic</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Mosque</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Blog</t>
+          <t>NGO office</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Bookmark</t>
+          <t>Oil facility</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Police station</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Checked mail</t>
+          <t>Power electricity</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>School</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CSV file</t>
+          <t>UN compound office</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>General infrastructure</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Delete account</t>
+          <t>University</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>DOCX file</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Airport military</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -5048,12 +5048,12 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Expand down</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Expand left</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Expand right</t>
+          <t>Ferry</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Expand up</t>
+          <t>Gas station</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Favourite</t>
+          <t>Helicopter</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Helipad</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Hidden</t>
+          <t>Truck</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Tunnel</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>UN vehicle</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>More options</t>
+          <t>Cell tower</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Next item</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Not secured</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Fax</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Out of platform</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Mobile phone</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>PDF file</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Previous item</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Remote support</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>Satellite dish</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -5473,12 +5473,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Remove document</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Walkie talkie</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>UX UI</t>
+          <t>Telecommunications and technology</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Work from home</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Secured</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Add document</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>See</t>
+          <t>AI chat</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Selected</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Blog</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Bookmark</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>Checked mail</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>CSV file</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Delete account</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>DOCX file</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Validate account</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>XLSX file</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>ZIP compressed</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Bacteria</t>
+          <t>Exit cancel</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Case management</t>
+          <t>Expand down</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Expand left</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Expand right</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Handwashing</t>
+          <t>Expand up</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Health worker</t>
+          <t>Favourite</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Hospital bed</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Infected</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Infection control</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Life saving</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t>Hidden</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Not infected</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Physical distancing</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Respiratory</t>
+          <t>More options</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Sanitizer</t>
+          <t>Next item</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Not secured</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Ventilator</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Out of platform</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Airport closed</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Border closed</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Bridge closed</t>
+          <t>PDF file</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Building closed</t>
+          <t>Previous item</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>House lockdown</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Location lockdown</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Market closed</t>
+          <t>Remove document</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Port closed</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Road closed</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -6289,12 +6289,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Lockdown</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>School closed</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -6306,12 +6306,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Advocacy</t>
+          <t>Secured</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>See</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Assessment</t>
+          <t>Selected</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Cash transfer</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Civil military coordination</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Community engagement</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Trending</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Fund</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Gap analysis</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Humanitarian programme cycle</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Information management</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Validate account</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>Warning error</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>XLSX file</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>UX UI</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>ZIP compressed</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Bacteria</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Case management</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -6629,12 +6629,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Needs assessment</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Partnership</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Handwashing</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Preparedness</t>
+          <t>Health worker</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Public information</t>
+          <t>Hospital bed</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Infected</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Infection control</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -6748,12 +6748,12 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Scale down operation</t>
+          <t>Laboratory</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Scale up operation</t>
+          <t>Life saving</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Search and rescue</t>
+          <t>Mask</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Services and tools</t>
+          <t>Not infected</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Staff management</t>
+          <t>Physical distancing</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Top ranking</t>
+          <t>Respiratory</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Activities strategy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Sanitizer</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Camp coordination and camp management</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Coordinated assessment</t>
+          <t>Ventilator</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Damaged affected</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Early recovery</t>
+          <t>Airport closed</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Emergency telecommunications</t>
+          <t>Border closed</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>Exit cancel</t>
+          <t>Bridge closed</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Food security</t>
+          <t>Building closed</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -6986,12 +6986,12 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Indigenous people</t>
+          <t>House lockdown</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Logistics and telecommunications</t>
+          <t>Location lockdown</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Sexual and reproductive health</t>
+          <t>Market closed</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>Shelter, land and site coordination</t>
+          <t>Port closed</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>Warning error</t>
+          <t>Road closed</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -7071,12 +7071,12 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Lockdown</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Water sanitation and hygiene</t>
+          <t>School closed</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
